--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-43.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>447.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.1%</t>
+          <t>-632.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.9%</t>
+          <t>-283.4%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-178.2%</t>
+          <t>-178.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1976"/>
+  <dimension ref="A1:G1978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919914</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318098</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.76264747767452</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.632335295945057</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983933019872959</v>
+        <v>0.9606281600596946</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.539105525777115</v>
+        <v>-4.633518380596119</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9896958435713969</v>
+        <v>0.9519307016437955</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3588954571964666</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.415977818783032</v>
+        <v>-4.510390673602036</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.039498799402132</v>
+        <v>1.00173365747453</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3588954571964666</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.323167337332173</v>
+        <v>-4.417580192151176</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.005895683873841</v>
+        <v>0.9681305419462398</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2660849757456073</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.274604285111143</v>
+        <v>-4.369017139930146</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.027194380686854</v>
+        <v>0.9894292387592527</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2175219235245771</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.161933066874893</v>
+        <v>-4.256345921693896</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.067338576493077</v>
+        <v>1.029573434565476</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1048507052883269</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.04955606569222</v>
+        <v>-4.143968920511223</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117780672796813</v>
+        <v>1.080015530869212</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1048507052883269</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.24779063457895</v>
+        <v>-4.342203489397954</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.04998404701066</v>
+        <v>1.012218905083059</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3030852741750575</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.330791915604229</v>
+        <v>-4.425204770423233</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8551392546012018</v>
+        <v>0.8173741126736005</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3216561587022312</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.457858921911217</v>
+        <v>-4.552271776730221</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9244621127976123</v>
+        <v>0.886696970870011</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3216561587022312</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.54445750489232</v>
+        <v>-4.638870359711324</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9043357057074941</v>
+        <v>0.8665705637798928</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3216561587022312</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.506073842334169</v>
+        <v>-4.600486697153173</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9171086120731231</v>
+        <v>0.8793434701455218</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2832724961440801</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.328957512299003</v>
+        <v>-4.423370367118006</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9846841729324916</v>
+        <v>0.9469190310048903</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2832724961440801</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.29925538832271</v>
+        <v>-4.393668243141713</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9972484142849221</v>
+        <v>0.9594832723573208</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2877426213593934</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.119879967083942</v>
+        <v>-4.214292821902945</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.062785558086843</v>
+        <v>1.025020416159242</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1309658631886748</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.164894180604549</v>
+        <v>-4.259307035423552</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.025587328010191</v>
+        <v>0.9878221860825893</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1613147585032794</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.431898690876984</v>
+        <v>-4.526311545695987</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9244770862401623</v>
+        <v>0.8867119443125611</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3556777965462279</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.533096472314156</v>
+        <v>-4.62750932713316</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8832018955617946</v>
+        <v>0.8454367536341933</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4240866100915471</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.500620886143384</v>
+        <v>-4.595033740962387</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8937920915844204</v>
+        <v>0.8560269496568189</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4240866100915471</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.481582758436087</v>
+        <v>-4.57599561325509</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8979320618755842</v>
+        <v>0.8601669199479829</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4822702214227417</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.512709389586705</v>
+        <v>-4.607122244405708</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.063063278354017</v>
+        <v>1.025298136426416</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4822702214227417</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.565029770187497</v>
+        <v>-4.6594426250065</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.042968455099834</v>
+        <v>1.005203313172233</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4473233614138695</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.709352676112416</v>
+        <v>-4.803765530931419</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9912478231267925</v>
+        <v>0.9534826811991912</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4473233614138695</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.561609705877413</v>
+        <v>-4.656022560696417</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.129497659012816</v>
+        <v>1.091732517085214</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2795160041789864</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.663624388408635</v>
+        <v>-4.758037243227638</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.091485407531808</v>
+        <v>1.053720265604207</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2795160041789864</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.527015044314542</v>
+        <v>-4.621427899133545</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.146791493561103</v>
+        <v>1.109026351633502</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1429066600848939</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.669780377137192</v>
+        <v>-4.764193231956195</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.088765837172154</v>
+        <v>1.051000695244552</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2856719929075443</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.60748237836107</v>
+        <v>-4.701895233180073</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.180020590479423</v>
+        <v>1.142255448551822</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2856719929075443</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.405692180695912</v>
+        <v>-4.500105035514915</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9693175419348847</v>
+        <v>0.9315524000072832</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.08765380073838991</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.345801499053318</v>
+        <v>-4.440214353872322</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.063564046914097</v>
+        <v>1.025798904986496</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.02776311909579643</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.443542043678293</v>
+        <v>-4.537954898497296</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.039095565180151</v>
+        <v>1.00133042325255</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.04365239722877662</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.619879803801222</v>
+        <v>-4.714292658620225</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9670964419556509</v>
+        <v>0.9293313000280496</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.219990157351706</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.619190431639999</v>
+        <v>-4.713603286459002</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9658638088600688</v>
+        <v>0.9280986669324676</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.219990157351706</v>
@@ -46993,22 +46993,68 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.625761396694592</v>
+        <v>-4.720174251513595</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.963098290273668</v>
+        <v>0.9253331483460667</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2265611224062989</v>
       </c>
       <c r="G1976" t="n">
         <v>2.677822599821473</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="2" t="n">
+        <v>45439</v>
+      </c>
+      <c r="B1977" t="n">
+        <v>3.821591150863224</v>
+      </c>
+      <c r="C1977" t="n">
+        <v>2.813759273265252</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>-4.712220281218823</v>
+      </c>
+      <c r="E1977" t="n">
+        <v>0.9285147364639754</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>-0.2265611224062989</v>
+      </c>
+      <c r="G1977" t="n">
+        <v>2.677822599821473</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="B1978" t="n">
+        <v>3.715047755756957</v>
+      </c>
+      <c r="C1978" t="n">
+        <v>2.682296671002711</v>
+      </c>
+      <c r="D1978" t="n">
+        <v>-4.712220281218823</v>
+      </c>
+      <c r="E1978" t="n">
+        <v>0.9285147364639754</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>-0.2265611224062989</v>
+      </c>
+      <c r="G1978" t="n">
+        <v>2.675360467989079</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.3%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.8%</t>
+          <t>-623.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.4%</t>
+          <t>-282.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-178.5%</t>
+          <t>-162.6%</t>
         </is>
       </c>
     </row>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.131236680557597</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.09601707701221551</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.745308851092495</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.108673703193408</v>
+        <v>2.084051369902101</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.126604167304624</v>
       </c>
       <c r="D1905" t="n">
         <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>-0.04773940081283357</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.613033377461608</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.183406474118967</v>
+        <v>2.15878414082766</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.129419227992261</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.744368184836123</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>0.03131552974406393</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.422433702788455</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.275959006319188</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.142325569215919</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.495368386152542</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.1438217904411552</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.422433702788455</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.288865347542846</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.0143496396167</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.600958375925646</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>-0.02639013506730592</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.528023692561559</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.097535424079765</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.062893981493787</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.619693278044243</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>0.01466024596234172</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.528023692561559</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.146079765956851</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.943015058805619</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.471753236636644</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>-0.04604266016278613</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.507702776653002</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>2.038393392813818</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.934301072552141</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.45459508650535</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>-0.04789338636374652</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.490544626521707</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>2.039974296639117</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.927340460457048</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.411046679734659</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>-0.03743463575056349</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.490544626521707</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>2.033013684544024</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.941802814838191</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.168898286280801</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.07388707601212285</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.490544626521707</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>2.047476038925167</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.936334935297386</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.105668914512453</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1183332784699656</v>
+        <v>0.0937109451786573</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.490544626521707</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>2.042008159384362</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.933833029307963</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.982377779695322</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1651478264073947</v>
+        <v>0.1405254931160864</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.367253491704577</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.113480934285217</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919914</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.941534007545288</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.961228580791879</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.181308484206097</v>
+        <v>0.1566861509147888</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.346104292801134</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.133871431864608</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.937314715892339</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.717463138808434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2745953693465255</v>
+        <v>0.2499730360552173</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.346104292801134</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.129652140211659</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.939439029812354</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.570566111090564</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3354784943536897</v>
+        <v>0.3108561610623815</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.298446050822545</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.160371399318827</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.932181104796057</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.320715717141489</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4281607269170218</v>
+        <v>0.4035383936257135</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.298446050822545</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.15311347430253</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.935780228316705</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.144823624674057</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5021166874246434</v>
+        <v>0.4774943541333352</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.298446050822545</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.156712597823178</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.949107734371259</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.973377161651594</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5840227786881824</v>
+        <v>0.5594004453968742</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.126999587800082</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.27290798169121</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.948128211987556</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.748344161982771</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6730564561720089</v>
+        <v>0.6484341228807007</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9019665881312596</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.406948259108801</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.952823013041873</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.684708419748836</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7032055541198998</v>
+        <v>0.6785832208285916</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8383308458973251</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.449824505503479</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.934017271825669</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.591708378542938</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7215998293860548</v>
+        <v>0.6969774960947466</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8383308458973251</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.431018764287274</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.935760348450546</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.351277881738078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8195151047328761</v>
+        <v>0.7948927714415679</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5979003490924648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.577020138995068</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.939689662285367</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.279035313566883</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8523414458361742</v>
+        <v>0.827719112544866</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5979003490924648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.580949452829888</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.940368246202707</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.226036991285495</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8742193586660694</v>
+        <v>0.8495970253747611</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.542564090090526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.614829792148391</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.9373663174227</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.117232105805768</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9147393840779539</v>
+        <v>0.8901170507866456</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.542564090090526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.611827863368385</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.938945354433314</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.897211307768758</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004326740303372</v>
+        <v>0.979704407012064</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4013442450225457</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.698138807419787</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.954839537235137</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.76434361870548</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073367998730506</v>
+        <v>1.048745665439198</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4013442450225457</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.71403299022161</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.955985381675439</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.60482851518611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138319884578556</v>
+        <v>1.113697551287248</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2418291415031758</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.810887896773534</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.966073484236879</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.460156370086373</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206276845179891</v>
+        <v>1.181654511888583</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.09715699640343839</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.907779286394816</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942108</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.952110975638305</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.520031197444065</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16836440563824</v>
+        <v>1.143742072346932</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1570318237611305</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.857891881381627</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.974511468960871</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.433231699665056</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.22548469807241</v>
+        <v>1.200862364781102</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1570318237611305</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.880292374704193</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.974583870334283</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.435701406126862</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.2245692168611</v>
+        <v>1.199946883569791</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1595015302229367</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.878882952200521</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.985590792808985</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.504071592450872</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208228064806197</v>
+        <v>1.183605731514889</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1502258311867217</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.895455294096953</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.976027501440877</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.612609773367006</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155249501071635</v>
+        <v>1.130627167780327</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1502258311867217</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.885892002728844</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.800737066481263</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.643602932695711</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9675618023805399</v>
+        <v>0.9429394690892317</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1502258311867217</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.710601567769231</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.805304298473051</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.468128672903243</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042318738289315</v>
+        <v>1.017696404998007</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1502258311867217</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.715168799761019</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.781046327234258</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.579064925544492</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9736862659940226</v>
+        <v>0.9490639327027144</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1502258311867217</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.690910828522226</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.784177712454164</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.782091503087725</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8956070201966349</v>
+        <v>0.8709846869053266</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3532524087299551</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.572226267216191</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.794350098886296</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.624165904152432</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689496462028844</v>
+        <v>0.9443273129115761</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.582398653648323</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.789296369460156</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.632335295945057</v>
+        <v>-4.537922441126054</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9606281600596946</v>
+        <v>0.9737709686959877</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.577344924222184</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.781072144904682</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.633518380596119</v>
+        <v>-4.539105525777115</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9519307016437955</v>
+        <v>0.9650735102800887</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3588954571964666</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.59035720387811</v>
+        <v>2.565734870586802</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.781624017937784</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.510390673602036</v>
+        <v>-4.415977818783032</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.00173365747453</v>
+        <v>1.014876466110823</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3588954571964666</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.590909076911212</v>
+        <v>2.566286743619904</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.710896709829149</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.417580192151176</v>
+        <v>-4.323167337332173</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9681305419462398</v>
+        <v>0.9812733505825328</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2660849757456073</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.575868057673093</v>
+        <v>2.551245724381785</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.71277018575375</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.369017139930146</v>
+        <v>-4.274604285111143</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9894292387592527</v>
+        <v>1.002572047395546</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2175219235245771</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.606879364930312</v>
+        <v>2.582257031639004</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.707845894265473</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.256345921693896</v>
+        <v>-4.161933066874893</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.029573434565476</v>
+        <v>1.042716243201769</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1048507052883269</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.669557804383786</v>
+        <v>2.644935471092477</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.71333719009614</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.143968920511223</v>
+        <v>-4.04955606569222</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.080015530869212</v>
+        <v>1.093158339505505</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1048507052883269</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.675049100214453</v>
+        <v>2.650426766923144</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.724834391864679</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.342203489397954</v>
+        <v>-4.24779063457895</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.012218905083059</v>
+        <v>1.025361713719352</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3030852741750575</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.567605560650954</v>
+        <v>2.542983227359645</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.563190111865333</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.425204770423233</v>
+        <v>-4.330791915604229</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8173741126736005</v>
+        <v>0.8305169213098935</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3216561587022312</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.394818749935302</v>
+        <v>2.370196416643994</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.683339772584538</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.552271776730221</v>
+        <v>-4.457858921911217</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.886696970870011</v>
+        <v>0.899839779506304</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3216561587022312</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.514968410654508</v>
+        <v>2.4903460773632</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.697852798686861</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.638870359711324</v>
+        <v>-4.54445750489232</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8665705637798928</v>
+        <v>0.8797133724161859</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3216561587022312</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.529481436756831</v>
+        <v>2.504859103465523</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.69527224002923</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.600486697153173</v>
+        <v>-4.506073842334169</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8793434701455218</v>
+        <v>0.8924862787818149</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2832724961440801</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.54993107563409</v>
+        <v>2.525308742342782</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.692001268874532</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.423370367118006</v>
+        <v>-4.328957512299003</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9469190310048903</v>
+        <v>0.9600618396411833</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2832724961440801</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.546660104479392</v>
+        <v>2.522037771188084</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.692684660636445</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.393668243141713</v>
+        <v>-4.29925538832271</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9594832723573208</v>
+        <v>0.9726260809936138</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2877426213593934</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.544661421112117</v>
+        <v>2.520039087820809</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.686471635942859</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.214292821902945</v>
+        <v>-4.119879967083942</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.025020416159242</v>
+        <v>1.038163224795535</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1309658631886748</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.632514451320963</v>
+        <v>2.607892118029655</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.667279091274449</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.259307035423552</v>
+        <v>-4.164894180604549</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9878221860825893</v>
+        <v>1.000964994718882</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1613147585032794</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.59511256946379</v>
+        <v>2.570490236172482</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.672970653613395</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.526311545695987</v>
+        <v>-4.431898690876984</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8867119443125611</v>
+        <v>0.8998547529488541</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3556777965462279</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.484186308976966</v>
+        <v>2.459563975685658</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.672174575509896</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.62750932713316</v>
+        <v>-4.533096472314156</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8454367536341933</v>
+        <v>0.8585795622704864</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4240866100915471</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.442344942746276</v>
+        <v>2.417722609454968</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.669774537064213</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.595033740962387</v>
+        <v>-4.500620886143384</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8560269496568189</v>
+        <v>0.8691697582931122</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4240866100915471</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.439944904300593</v>
+        <v>2.415322571009285</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.666299256272458</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.57599561325509</v>
+        <v>-4.481582758436087</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8601669199479829</v>
+        <v>0.8733097285842759</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4822702214227417</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.401559456710121</v>
+        <v>2.376937123418813</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.843881125211138</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.607122244405708</v>
+        <v>-4.512709389586705</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.025298136426416</v>
+        <v>1.038440945062709</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4822702214227417</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.579141325648802</v>
+        <v>2.554518992357494</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.844714454197272</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.6594426250065</v>
+        <v>-4.565029770187497</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.005203313172233</v>
+        <v>1.018346121808526</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4473233614138695</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.600942770640259</v>
+        <v>2.576320437348951</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.850722984594198</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.803765530931419</v>
+        <v>-4.709352676112416</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9534826811991912</v>
+        <v>0.9666254898354842</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4473233614138695</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.606951301037185</v>
+        <v>2.582328967745877</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.92987563238622</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.656022560696417</v>
+        <v>-4.561609705877413</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.091732517085214</v>
+        <v>1.104875325721507</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2795160041789864</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.786788363170137</v>
+        <v>2.762166029878828</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.932669253917701</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.758037243227638</v>
+        <v>-4.663624388408635</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.053720265604207</v>
+        <v>1.0668630742405</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2795160041789864</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.789581984701618</v>
+        <v>2.764959651410309</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.933331602309359</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.621427899133545</v>
+        <v>-4.527015044314542</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.109026351633502</v>
+        <v>1.122169160269795</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1429066600848939</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.872209939549732</v>
+        <v>2.847587606258423</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.932412079049469</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.764193231956195</v>
+        <v>-4.669780377137192</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.051000695244552</v>
+        <v>1.064143503880845</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2856719929075443</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.785631216596252</v>
+        <v>2.761008883304943</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.99874763284629</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.701895233180073</v>
+        <v>-4.60748237836107</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.142255448551822</v>
+        <v>1.155398257188115</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2856719929075443</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.851966770393072</v>
+        <v>2.827344437101764</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.707328505235688</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.500105035514915</v>
+        <v>-4.405692180695912</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9315524000072832</v>
+        <v>0.9446952086435765</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.08765380073838991</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.679358558083963</v>
+        <v>2.654736224792654</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.777618737557864</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.440214353872322</v>
+        <v>-4.345801499053318</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.025798904986496</v>
+        <v>1.038941713622789</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.02776311909579643</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.785583199391694</v>
+        <v>2.760960866100386</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.792246473673907</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.537954898497296</v>
+        <v>-4.443542043678293</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.00133042325255</v>
+        <v>1.014473231888843</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.04365239722877662</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.79067736862795</v>
+        <v>2.766055035336641</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.790782454498579</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.714292658620225</v>
+        <v>-4.619879803801222</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9293313000280496</v>
+        <v>0.9424741086643427</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.219990157351706</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.683410693378864</v>
+        <v>2.658788360087556</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.789274072538507</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.713603286459002</v>
+        <v>-4.619190431639999</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9280986669324676</v>
+        <v>0.9412414755687606</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.219990157351706</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.681902311418793</v>
+        <v>2.657279978127484</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.789136939973944</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.720174251513595</v>
+        <v>-4.625761396694592</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9253331483460667</v>
+        <v>0.9384759569823597</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2265611224062989</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.677822599821473</v>
+        <v>2.653200266530165</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.789136939973944</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.712220281218823</v>
+        <v>-4.617807426399819</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9285147364639754</v>
+        <v>0.9416575451002687</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2265611224062989</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.677822599821473</v>
+        <v>2.653200266530165</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.715047755756957</v>
+        <v>3.82539319141264</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.682296671002711</v>
+        <v>2.840914442617851</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.712220281218823</v>
+        <v>-4.617807426399819</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9285147364639754</v>
+        <v>0.9416575451002687</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.2265611224062989</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.675360467989079</v>
+        <v>2.833978239604218</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>447.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.4%</t>
+          <t>-640.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>181.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-273.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.0%</t>
+          <t>-140.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.6%</t>
+          <t>-249.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-165.3%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440637</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608603</v>
+        <v>3.490059241608605</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410276</v>
+        <v>3.485878594410277</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764401</v>
+        <v>3.480692492764403</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371601439059</v>
+        <v>3.493716014390593</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297404</v>
+        <v>3.492101641297407</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322548</v>
+        <v>3.573674025322551</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158926</v>
+        <v>3.600038265158928</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940723</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.131236680557597</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-8.151009267384103</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09601707701221551</v>
+        <v>-0.1295234507097915</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.745308851092495</v>
+        <v>-1.76866612403213</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.084051369902101</v>
+        <v>2.070037006138319</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
         <v>3.126604167304624</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-8.018733793753215</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04773940081283357</v>
+        <v>-0.0812457745104096</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.613033377461608</v>
+        <v>-1.636390650401244</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.15878414082766</v>
+        <v>2.144769777063878</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105958</v>
       </c>
       <c r="C1906" t="n">
         <v>3.129419227992261</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.828134119080063</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03131552974406393</v>
+        <v>-0.002190843953511656</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.445790975728091</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.275959006319188</v>
+        <v>2.261944642555406</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960993</v>
       </c>
       <c r="C1907" t="n">
         <v>3.142325569215919</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.579134320396482</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1438217904411552</v>
+        <v>0.1103154167435791</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.445790975728091</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.288865347542846</v>
+        <v>2.274850983779065</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.0143496396167</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.684724310169586</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02639013506730592</v>
+        <v>-0.05989650876488151</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.551380965501195</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.097535424079765</v>
+        <v>2.083521060315983</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.062893981493787</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.703459212288183</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01466024596234172</v>
+        <v>-0.01884612773523386</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.551380965501195</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.146079765956851</v>
+        <v>2.13206540219307</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.943015058805619</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.555519170880584</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04604266016278613</v>
+        <v>-0.07954903386036172</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.531060049592637</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.038393392813818</v>
+        <v>2.024379029050037</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.934301072552141</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.538361020749289</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04789338636374652</v>
+        <v>-0.08139976006132255</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.513901899461343</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.039974296639117</v>
+        <v>2.025959932875335</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
         <v>2.927340460457048</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.494812613978599</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03743463575056349</v>
+        <v>-0.07094100944813952</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.513901899461343</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.033013684544024</v>
+        <v>2.018999320780242</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
         <v>2.941802814838191</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.252664220524741</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.07388707601212285</v>
+        <v>0.04038070231454682</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.513901899461343</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.047476038925167</v>
+        <v>2.033461675161385</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722823</v>
       </c>
       <c r="C1914" t="n">
         <v>2.936334935297386</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.105668914512453</v>
+        <v>-7.189434848756393</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0937109451786573</v>
+        <v>0.06020457148108127</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.513901899461343</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.042008159384362</v>
+        <v>2.02799379562058</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792053</v>
       </c>
       <c r="C1915" t="n">
         <v>2.933833029307963</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.982377779695322</v>
+        <v>-7.066143713939262</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1405254931160864</v>
+        <v>0.1070191194185104</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.390610764644213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.113480934285217</v>
+        <v>2.099466570521435</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919915</v>
       </c>
       <c r="C1916" t="n">
         <v>2.941534007545288</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.961228580791879</v>
+        <v>-7.044994515035818</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1566861509147888</v>
+        <v>0.1231797772172132</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.369461565740769</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.133871431864608</v>
+        <v>2.119857068100827</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.7483284083181</v>
       </c>
       <c r="C1917" t="n">
         <v>2.937314715892339</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717463138808434</v>
+        <v>-6.801229073052374</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2499730360552173</v>
+        <v>0.2164666623576417</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.369461565740769</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.129652140211659</v>
+        <v>2.115637776447877</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.939439029812354</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.570566111090564</v>
+        <v>-6.654332045334504</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3108561610623815</v>
+        <v>0.2773497873648054</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.321803323762181</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.160371399318827</v>
+        <v>2.146357035555046</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.932181104796057</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.320715717141489</v>
+        <v>-6.40448165138543</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4035383936257135</v>
+        <v>0.3700320199281375</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.321803323762181</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.15311347430253</v>
+        <v>2.139099110538748</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.935780228316705</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.144823624674057</v>
+        <v>-6.228589558917998</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4774943541333352</v>
+        <v>0.4439879804357592</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.321803323762181</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.156712597823178</v>
+        <v>2.142698234059397</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.949107734371259</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.973377161651594</v>
+        <v>-6.057143095895534</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5594004453968742</v>
+        <v>0.5258940716992981</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.150356860739718</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.27290798169121</v>
+        <v>2.258893617927428</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.948128211987556</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.748344161982771</v>
+        <v>-5.832110096226711</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6484341228807007</v>
+        <v>0.6149277491831242</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-0.9253238610708953</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.406948259108801</v>
+        <v>2.392933895345019</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.952823013041873</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.684708419748836</v>
+        <v>-5.768474353992777</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6785832208285916</v>
+        <v>0.6450768471310155</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8616881188369607</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.449824505503479</v>
+        <v>2.435810141739697</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.934017271825669</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.591708378542938</v>
+        <v>-5.675474312786879</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6969774960947466</v>
+        <v>0.6634711223971701</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8616881188369607</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.431018764287274</v>
+        <v>2.417004400523493</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.935760348450546</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.351277881738078</v>
+        <v>-5.435043815982018</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7948927714415679</v>
+        <v>0.7613863977439919</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6212576220321004</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.577020138995068</v>
+        <v>2.563005775231286</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.939689662285367</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.279035313566883</v>
+        <v>-5.362801247810824</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.827719112544866</v>
+        <v>0.7942127388472899</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6212576220321004</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.580949452829888</v>
+        <v>2.566935089066106</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.940368246202707</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.226036991285495</v>
+        <v>-5.309802925529436</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8495970253747611</v>
+        <v>0.8160906516771851</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.5659213630301616</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.614829792148391</v>
+        <v>2.60081542838461</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.9373663174227</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.117232105805768</v>
+        <v>-5.200998040049709</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8901170507866456</v>
+        <v>0.8566106770890691</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.5659213630301616</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.611827863368385</v>
+        <v>2.597813499604603</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.938945354433314</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897211307768758</v>
+        <v>-4.980977242012698</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.979704407012064</v>
+        <v>0.9461980333144877</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.4247015179621814</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.698138807419787</v>
+        <v>2.684124443656005</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.954839537235137</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.76434361870548</v>
+        <v>-4.84810955294942</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.048745665439198</v>
+        <v>1.015239291741622</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.4247015179621814</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.71403299022161</v>
+        <v>2.700018626457829</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.955985381675439</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.60482851518611</v>
+        <v>-4.688594449430051</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.113697551287248</v>
+        <v>1.080191177589672</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.2651864144428114</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.810887896773534</v>
+        <v>2.796873533009753</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.966073484236879</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460156370086373</v>
+        <v>-4.543922304330313</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.181654511888583</v>
+        <v>1.148148138191007</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.120514269343074</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.907779286394816</v>
+        <v>2.893764922631035</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.952110975638305</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.520031197444065</v>
+        <v>-4.603797131688006</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.143742072346932</v>
+        <v>1.110235698649356</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1803890967007661</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.857891881381627</v>
+        <v>2.843877517617845</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.974511468960871</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433231699665056</v>
+        <v>-4.516997633908996</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.200862364781102</v>
+        <v>1.167355991083525</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1803890967007661</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.880292374704193</v>
+        <v>2.866278010940412</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.974583870334283</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435701406126862</v>
+        <v>-4.519467340370802</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.199946883569791</v>
+        <v>1.166440509872215</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.1828588031625723</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.878882952200521</v>
+        <v>2.86486858843674</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.985590792808985</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504071592450872</v>
+        <v>-4.587837526694813</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.183605731514889</v>
+        <v>1.150099357817313</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1735831041263574</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.895455294096953</v>
+        <v>2.881440930333171</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.976027501440877</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612609773367006</v>
+        <v>-4.696375707610946</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130627167780327</v>
+        <v>1.097120794082751</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1735831041263574</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.885892002728844</v>
+        <v>2.871877638965063</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.800737066481263</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643602932695711</v>
+        <v>-4.727368866939652</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9429394690892317</v>
+        <v>0.9094330953916554</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1735831041263574</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.710601567769231</v>
+        <v>2.696587204005449</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.805304298473051</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468128672903243</v>
+        <v>-4.551894607147183</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.017696404998007</v>
+        <v>0.9841900313004306</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1735831041263574</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.715168799761019</v>
+        <v>2.701154435997237</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.781046327234258</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579064925544492</v>
+        <v>-4.662830859788432</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9490639327027144</v>
+        <v>0.9155575590051381</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1735831041263574</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.690910828522226</v>
+        <v>2.676896464758444</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.784177712454164</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782091503087725</v>
+        <v>-4.865857437331665</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8709846869053266</v>
+        <v>0.8374783132077503</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3766096816695907</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.572226267216191</v>
+        <v>2.55821190345241</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.794350098886296</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624165904152432</v>
+        <v>-4.707931838396372</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9443273129115761</v>
+        <v>0.9108209392140001</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3766096816695907</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.582398653648323</v>
+        <v>2.568384289884542</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.789296369460156</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.621688375369994</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9737709686959877</v>
+        <v>0.9402645949984114</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3766096816695907</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.577344924222184</v>
+        <v>2.563330560458402</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.781072144904682</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.539105525777115</v>
+        <v>-4.622871460021056</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9650735102800887</v>
+        <v>0.9315671365825124</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3588954571964666</v>
+        <v>-0.3822527301361023</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.565734870586802</v>
+        <v>2.551720506823021</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.781624017937784</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.415977818783032</v>
+        <v>-4.499743753026973</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.014876466110823</v>
+        <v>0.9813700924132471</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3588954571964666</v>
+        <v>-0.3822527301361023</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.566286743619904</v>
+        <v>2.552272379856122</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809504</v>
       </c>
       <c r="C1946" t="n">
         <v>2.710896709829149</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.323167337332173</v>
+        <v>-4.406933271576113</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9812733505825328</v>
+        <v>0.9477669768849566</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2660849757456073</v>
+        <v>-0.2894422486852429</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.551245724381785</v>
+        <v>2.537231360618004</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.71277018575375</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.274604285111143</v>
+        <v>-4.358370219355083</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.002572047395546</v>
+        <v>0.9690656736979695</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2175219235245771</v>
+        <v>-0.2408791964642127</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.582257031639004</v>
+        <v>2.568242667875223</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.707845894265473</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.161933066874893</v>
+        <v>-4.245699001118833</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.042716243201769</v>
+        <v>1.009209869504192</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1048507052883269</v>
+        <v>-0.1282079782279625</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.644935471092477</v>
+        <v>2.630921107328696</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.71333719009614</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.04955606569222</v>
+        <v>-4.13332199993616</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.093158339505505</v>
+        <v>1.059651965807929</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1048507052883269</v>
+        <v>-0.1282079782279625</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.650426766923144</v>
+        <v>2.636412403159363</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.724834391864679</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.24779063457895</v>
+        <v>-4.331556568822891</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.025361713719352</v>
+        <v>0.9918553400217758</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3030852741750575</v>
+        <v>-0.3264425471146931</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.542983227359645</v>
+        <v>2.528968863595864</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.563190111865333</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.330791915604229</v>
+        <v>-4.41455784984817</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8305169213098935</v>
+        <v>0.7970105476123175</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3450134316418669</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.370196416643994</v>
+        <v>2.356182052880213</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.683339772584538</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.457858921911217</v>
+        <v>-4.541624856155158</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.899839779506304</v>
+        <v>0.8663334058087278</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3450134316418669</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.4903460773632</v>
+        <v>2.476331713599418</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.697852798686861</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.54445750489232</v>
+        <v>-4.628223439136261</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8797133724161859</v>
+        <v>0.8462069987186096</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3450134316418669</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.504859103465523</v>
+        <v>2.490844739701741</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.69527224002923</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.506073842334169</v>
+        <v>-4.58983977657811</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8924862787818149</v>
+        <v>0.8589799050842388</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2832724961440801</v>
+        <v>-0.3066297690837157</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.525308742342782</v>
+        <v>2.511294378579001</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.692001268874532</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.328957512299003</v>
+        <v>-4.412723446542944</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9600618396411833</v>
+        <v>0.926555465943607</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2832724961440801</v>
+        <v>-0.3066297690837157</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.522037771188084</v>
+        <v>2.508023407424303</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.692684660636445</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.29925538832271</v>
+        <v>-4.38302132256665</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9726260809936138</v>
+        <v>0.9391197072960376</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2877426213593934</v>
+        <v>-0.3110998942990291</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.520039087820809</v>
+        <v>2.506024724057028</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.686471635942859</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.119879967083942</v>
+        <v>-4.203645901327882</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.038163224795535</v>
+        <v>1.004656851097959</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1309658631886748</v>
+        <v>-0.1543231361283104</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.607892118029655</v>
+        <v>2.593877754265873</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.667279091274449</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.164894180604549</v>
+        <v>-4.248660114848489</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.000964994718882</v>
+        <v>0.9674586210213061</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1613147585032794</v>
+        <v>-0.184672031442915</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.570490236172482</v>
+        <v>2.5564758724087</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.672970653613395</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.431898690876984</v>
+        <v>-4.515664625120924</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8998547529488541</v>
+        <v>0.8663483792512778</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3556777965462279</v>
+        <v>-0.3790350694858636</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.459563975685658</v>
+        <v>2.445549611921877</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.672174575509896</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.533096472314156</v>
+        <v>-4.616862406558097</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8585795622704864</v>
+        <v>0.8250731885729103</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4240866100915471</v>
+        <v>-0.4474438830311828</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.417722609454968</v>
+        <v>2.403708245691187</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.669774537064213</v>
+        <v>2.820131857670783</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.500620886143384</v>
+        <v>-4.584386820387325</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8691697582931122</v>
+        <v>0.9860207052021057</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4240866100915471</v>
+        <v>-0.4474438830311828</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.415322571009285</v>
+        <v>2.551665527852073</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.666299256272458</v>
+        <v>2.816656576879028</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.481582758436087</v>
+        <v>-4.565348692680027</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8733097285842759</v>
+        <v>0.9901606754932695</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4822702214227417</v>
+        <v>-0.5056274943623773</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.376937123418813</v>
+        <v>2.513280080261602</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.843881125211138</v>
+        <v>2.994238445817708</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.512709389586705</v>
+        <v>-4.596475323830646</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.038440945062709</v>
+        <v>1.155291891971703</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4822702214227417</v>
+        <v>-0.5056274943623773</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.554518992357494</v>
+        <v>2.690861949200282</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.844714454197272</v>
+        <v>2.995071774803842</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.565029770187497</v>
+        <v>-4.648795704431437</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.018346121808526</v>
+        <v>1.135197068717519</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4473233614138695</v>
+        <v>-0.4706806343535052</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.576320437348951</v>
+        <v>2.712663394191739</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.850722984594198</v>
+        <v>3.001080305200768</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.709352676112416</v>
+        <v>-4.793118610356356</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9666254898354842</v>
+        <v>1.083476436744478</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4473233614138695</v>
+        <v>-0.4706806343535052</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.582328967745877</v>
+        <v>2.718671924588665</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.92987563238622</v>
+        <v>3.08023295299279</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.561609705877413</v>
+        <v>-4.645375640121354</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.104875325721507</v>
+        <v>1.221726272630501</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2795160041789864</v>
+        <v>-0.302873277118622</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.762166029878828</v>
+        <v>2.898508986721617</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.932669253917701</v>
+        <v>3.083026574524271</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.663624388408635</v>
+        <v>-4.747390322652575</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.0668630742405</v>
+        <v>1.183714021149493</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2795160041789864</v>
+        <v>-0.302873277118622</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.764959651410309</v>
+        <v>2.901302608253098</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.933331602309359</v>
+        <v>3.083688922915929</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.527015044314542</v>
+        <v>-4.610780978558482</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.122169160269795</v>
+        <v>1.239020107178789</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1429066600848939</v>
+        <v>-0.1662639330245295</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.847587606258423</v>
+        <v>2.983930563101211</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489062</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.932412079049469</v>
+        <v>3.082769399656039</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.669780377137192</v>
+        <v>-4.753546311381132</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.064143503880845</v>
+        <v>1.180994450789839</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2856719929075443</v>
+        <v>-0.3090292658471799</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.761008883304943</v>
+        <v>2.897351840147731</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.99874763284629</v>
+        <v>3.14910495345286</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.60748237836107</v>
+        <v>-4.69124831260501</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.155398257188115</v>
+        <v>1.272249204097109</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2856719929075443</v>
+        <v>-0.3090292658471799</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.827344437101764</v>
+        <v>2.963687393944552</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.707328505235688</v>
+        <v>2.857685825842258</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.405692180695912</v>
+        <v>-4.489458114939852</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9446952086435765</v>
+        <v>1.06154615555257</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.08765380073838991</v>
+        <v>-0.1110110736780255</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.654736224792654</v>
+        <v>2.791079181635443</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.777618737557864</v>
+        <v>2.927976058164433</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.345801499053318</v>
+        <v>-4.429567433297259</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.038941713622789</v>
+        <v>1.155792660531783</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.02776311909579643</v>
+        <v>-0.05112039203543206</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.760960866100386</v>
+        <v>2.897303822943174</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.792246473673907</v>
+        <v>2.942603794280477</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.443542043678293</v>
+        <v>-4.527307977922233</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.014473231888843</v>
+        <v>1.131324178797836</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.04365239722877662</v>
+        <v>-0.06700967016841225</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.766055035336641</v>
+        <v>2.90239799217943</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.790782454498579</v>
+        <v>2.941139775105149</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.619879803801222</v>
+        <v>-4.703645738045163</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9424741086643427</v>
+        <v>1.059325055573336</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.219990157351706</v>
+        <v>-0.2433474302913416</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.658788360087556</v>
+        <v>2.795131316930344</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.789274072538507</v>
+        <v>2.939631393145077</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.619190431639999</v>
+        <v>-4.70295636588394</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9412414755687606</v>
+        <v>1.058092422477754</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.219990157351706</v>
+        <v>-0.2433474302913416</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.657279978127484</v>
+        <v>2.793622934970272</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.789136939973944</v>
+        <v>2.939494260580513</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.625761396694592</v>
+        <v>-4.709527330938532</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9384759569823597</v>
+        <v>1.055326903891353</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.2499183953459346</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.653200266530165</v>
+        <v>2.789543223372953</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863228</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.789136939973944</v>
+        <v>2.939494260580513</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.617807426399819</v>
+        <v>-4.784479659420873</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9416575451002687</v>
+        <v>1.025345972498417</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.2499183953459346</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.653200266530165</v>
+        <v>2.789543223372953</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.82539319141264</v>
+        <v>3.719349573676941</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.840914442617851</v>
+        <v>2.813788084730972</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.617807426399819</v>
+        <v>-4.784479659420873</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9416575451002687</v>
+        <v>1.025345972498417</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.2499183953459346</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.833978239604218</v>
+        <v>2.80685188171734</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-46.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-52.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.2%</t>
+          <t>445.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.0%</t>
+          <t>-636.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>181.9%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-284.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-140.3%</t>
+          <t>-137.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.0%</t>
+          <t>-246.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>-181.1%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440637</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608605</v>
+        <v>3.490059241608603</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410277</v>
+        <v>3.485878594410276</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764403</v>
+        <v>3.480692492764401</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390593</v>
+        <v>3.49371601439059</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297407</v>
+        <v>3.492101641297404</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322551</v>
+        <v>3.573674025322548</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158928</v>
+        <v>3.600038265158926</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940723</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.131236680557597</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.151009267384103</v>
+        <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1295234507097915</v>
+        <v>-0.07139474372090771</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.76866612403213</v>
+        <v>-1.745308851092495</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.070037006138319</v>
+        <v>2.108673703193408</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.126604167304624</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.018733793753215</v>
+        <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0812457745104096</v>
+        <v>-0.02311706752152576</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.636390650401244</v>
+        <v>-1.613033377461608</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.144769777063878</v>
+        <v>2.183406474118967</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105958</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.129419227992261</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.828134119080063</v>
+        <v>-7.744368184836123</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.002190843953511656</v>
+        <v>0.05593786303537174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.445790975728091</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.261944642555406</v>
+        <v>2.300581339610495</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960993</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.142325569215919</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.579134320396482</v>
+        <v>-7.495368386152542</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1103154167435791</v>
+        <v>0.168444123732463</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.445790975728091</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.274850983779065</v>
+        <v>2.313487680834154</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.0143496396167</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.684724310169586</v>
+        <v>-7.600958375925646</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05989650876488151</v>
+        <v>-0.001767801775997668</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.551380965501195</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.083521060315983</v>
+        <v>2.122157757371073</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.062893981493787</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.703459212288183</v>
+        <v>-7.619693278044243</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01884612773523386</v>
+        <v>0.03928257925364997</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.551380965501195</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.13206540219307</v>
+        <v>2.170702099248159</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.943015058805619</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.555519170880584</v>
+        <v>-7.471753236636644</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07954903386036172</v>
+        <v>-0.02142032687147788</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.531060049592637</v>
+        <v>-1.507702776653002</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.024379029050037</v>
+        <v>2.063015726105126</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.934301072552141</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.538361020749289</v>
+        <v>-7.45459508650535</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08139976006132255</v>
+        <v>-0.02327105307243826</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.513901899461343</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.025959932875335</v>
+        <v>2.064596629930425</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.927340460457048</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.494812613978599</v>
+        <v>-7.411046679734659</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07094100944813952</v>
+        <v>-0.01281230245925524</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.513901899461343</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.018999320780242</v>
+        <v>2.057636017835332</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.941802814838191</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.252664220524741</v>
+        <v>-7.168898286280801</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04038070231454682</v>
+        <v>0.09850940930343111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.513901899461343</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.033461675161385</v>
+        <v>2.072098372216475</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722823</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.936334935297386</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.189434848756393</v>
+        <v>-7.105668914512453</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06020457148108127</v>
+        <v>0.1183332784699656</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.513901899461343</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.02799379562058</v>
+        <v>2.06663049267567</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792053</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.933833029307963</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.066143713939262</v>
+        <v>-6.982377779695322</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1070191194185104</v>
+        <v>0.1651478264073947</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.390610764644213</v>
+        <v>-1.367253491704577</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.099466570521435</v>
+        <v>2.138103267576525</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919915</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.941534007545288</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.044994515035818</v>
+        <v>-6.961228580791879</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1231797772172132</v>
+        <v>0.181308484206097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.369461565740769</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.119857068100827</v>
+        <v>2.158493765155916</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.7483284083181</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.937314715892339</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.801229073052374</v>
+        <v>-6.717463138808434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2164666623576417</v>
+        <v>0.2745953693465255</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.369461565740769</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.115637776447877</v>
+        <v>2.154274473502967</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.939439029812354</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.654332045334504</v>
+        <v>-6.570566111090564</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2773497873648054</v>
+        <v>0.3354784943536897</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.321803323762181</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.146357035555046</v>
+        <v>2.184993732610136</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.932181104796057</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.40448165138543</v>
+        <v>-6.320715717141489</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3700320199281375</v>
+        <v>0.4281607269170218</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.321803323762181</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.139099110538748</v>
+        <v>2.177735807593838</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.935780228316705</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.228589558917998</v>
+        <v>-6.144823624674057</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4439879804357592</v>
+        <v>0.5021166874246434</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.321803323762181</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.142698234059397</v>
+        <v>2.181334931114487</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.949107734371259</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.057143095895534</v>
+        <v>-5.973377161651594</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5258940716992981</v>
+        <v>0.5840227786881824</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.150356860739718</v>
+        <v>-1.126999587800082</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.258893617927428</v>
+        <v>2.297530314982518</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.948128211987556</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.832110096226711</v>
+        <v>-5.748344161982771</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6149277491831242</v>
+        <v>0.6730564561720089</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9253238610708953</v>
+        <v>-0.9019665881312596</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.392933895345019</v>
+        <v>2.431570592400109</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.952823013041873</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.768474353992777</v>
+        <v>-5.684708419748836</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6450768471310155</v>
+        <v>0.7032055541198998</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8616881188369607</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.435810141739697</v>
+        <v>2.474446838794787</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.934017271825669</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.675474312786879</v>
+        <v>-5.591708378542938</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6634711223971701</v>
+        <v>0.7215998293860548</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8616881188369607</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.417004400523493</v>
+        <v>2.455641097578583</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.935760348450546</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.435043815982018</v>
+        <v>-5.351277881738078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7613863977439919</v>
+        <v>0.8195151047328761</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6212576220321004</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.563005775231286</v>
+        <v>2.601642472286376</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.939689662285367</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.362801247810824</v>
+        <v>-5.279035313566883</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7942127388472899</v>
+        <v>0.8523414458361742</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6212576220321004</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.566935089066106</v>
+        <v>2.605571786121196</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.940368246202707</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.309802925529436</v>
+        <v>-5.226036991285495</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8160906516771851</v>
+        <v>0.8742193586660694</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5659213630301616</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.60081542838461</v>
+        <v>2.639452125439699</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.9373663174227</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.200998040049709</v>
+        <v>-5.117232105805768</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8566106770890691</v>
+        <v>0.9147393840779539</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5659213630301616</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.597813499604603</v>
+        <v>2.636450196659693</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.938945354433314</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.980977242012698</v>
+        <v>-4.897211307768758</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9461980333144877</v>
+        <v>1.004326740303372</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4247015179621814</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.684124443656005</v>
+        <v>2.722761140711095</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.954839537235137</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.84810955294942</v>
+        <v>-4.76434361870548</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.015239291741622</v>
+        <v>1.073367998730506</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4247015179621814</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.700018626457829</v>
+        <v>2.738655323512919</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.955985381675439</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.688594449430051</v>
+        <v>-4.60482851518611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.080191177589672</v>
+        <v>1.138319884578556</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2651864144428114</v>
+        <v>-0.2418291415031758</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.796873533009753</v>
+        <v>2.835510230064842</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.966073484236879</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.543922304330313</v>
+        <v>-4.460156370086373</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.148148138191007</v>
+        <v>1.206276845179891</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.120514269343074</v>
+        <v>-0.09715699640343839</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.893764922631035</v>
+        <v>2.932401619686125</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.952110975638305</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.603797131688006</v>
+        <v>-4.520031197444065</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.110235698649356</v>
+        <v>1.16836440563824</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1803890967007661</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.843877517617845</v>
+        <v>2.882514214672935</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.974511468960871</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.516997633908996</v>
+        <v>-4.433231699665056</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.167355991083525</v>
+        <v>1.22548469807241</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1803890967007661</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.866278010940412</v>
+        <v>2.904914707995502</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.974583870334283</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.519467340370802</v>
+        <v>-4.435701406126862</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.166440509872215</v>
+        <v>1.2245692168611</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1828588031625723</v>
+        <v>-0.1595015302229367</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.86486858843674</v>
+        <v>2.90350528549183</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.985590792808985</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.587837526694813</v>
+        <v>-4.504071592450872</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.150099357817313</v>
+        <v>1.208228064806197</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1735831041263574</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.881440930333171</v>
+        <v>2.920077627388261</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.976027501440877</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.696375707610946</v>
+        <v>-4.612609773367006</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.097120794082751</v>
+        <v>1.155249501071635</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1735831041263574</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.871877638965063</v>
+        <v>2.910514336020152</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.800737066481263</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.727368866939652</v>
+        <v>-4.643602932695711</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9094330953916554</v>
+        <v>0.9675618023805399</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1735831041263574</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.696587204005449</v>
+        <v>2.735223901060539</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.805304298473051</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.551894607147183</v>
+        <v>-4.468128672903243</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9841900313004306</v>
+        <v>1.042318738289315</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1735831041263574</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.701154435997237</v>
+        <v>2.739791133052327</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.781046327234258</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.662830859788432</v>
+        <v>-4.579064925544492</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9155575590051381</v>
+        <v>0.9736862659940226</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1735831041263574</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.676896464758444</v>
+        <v>2.715533161813534</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.784177712454164</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.865857437331665</v>
+        <v>-4.782091503087725</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8374783132077503</v>
+        <v>0.8956070201966349</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3766096816695907</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.55821190345241</v>
+        <v>2.596848600507499</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.794350098886296</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.707931838396372</v>
+        <v>-4.624165904152432</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9108209392140001</v>
+        <v>0.9689496462028844</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3766096816695907</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.568384289884542</v>
+        <v>2.607020986939632</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.789296369460156</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.621688375369994</v>
+        <v>-4.537922441126054</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9402645949984114</v>
+        <v>0.9983933019872959</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3766096816695907</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.563330560458402</v>
+        <v>2.601967257513492</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.781072144904682</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.622871460021056</v>
+        <v>-4.539105525777115</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9315671365825124</v>
+        <v>0.9896958435713969</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3822527301361023</v>
+        <v>-0.3588954571964666</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.551720506823021</v>
+        <v>2.59035720387811</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.781624017937784</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.499743753026973</v>
+        <v>-4.415977818783032</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9813700924132471</v>
+        <v>1.039498799402132</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3822527301361023</v>
+        <v>-0.3588954571964666</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.552272379856122</v>
+        <v>2.590909076911212</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.710896709829149</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.406933271576113</v>
+        <v>-4.323167337332173</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9477669768849566</v>
+        <v>1.005895683873841</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2894422486852429</v>
+        <v>-0.2660849757456073</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.537231360618004</v>
+        <v>2.575868057673093</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.71277018575375</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.358370219355083</v>
+        <v>-4.274604285111143</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9690656736979695</v>
+        <v>1.027194380686854</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2408791964642127</v>
+        <v>-0.2175219235245771</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.568242667875223</v>
+        <v>2.606879364930312</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.707845894265473</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.245699001118833</v>
+        <v>-4.161933066874893</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.009209869504192</v>
+        <v>1.067338576493077</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1282079782279625</v>
+        <v>-0.1048507052883269</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.630921107328696</v>
+        <v>2.669557804383786</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.71333719009614</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.13332199993616</v>
+        <v>-4.04955606569222</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.059651965807929</v>
+        <v>1.117780672796813</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1282079782279625</v>
+        <v>-0.1048507052883269</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.636412403159363</v>
+        <v>2.675049100214453</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.724834391864679</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.331556568822891</v>
+        <v>-4.24779063457895</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9918553400217758</v>
+        <v>1.04998404701066</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3264425471146931</v>
+        <v>-0.3030852741750575</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.528968863595864</v>
+        <v>2.567605560650954</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.563190111865333</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.41455784984817</v>
+        <v>-4.330791915604229</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7970105476123175</v>
+        <v>0.8551392546012018</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3450134316418669</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.356182052880213</v>
+        <v>2.394818749935302</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.683339772584538</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.541624856155158</v>
+        <v>-4.457858921911217</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8663334058087278</v>
+        <v>0.9244621127976123</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3450134316418669</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.476331713599418</v>
+        <v>2.514968410654508</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.697852798686861</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.628223439136261</v>
+        <v>-4.54445750489232</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8462069987186096</v>
+        <v>0.9043357057074941</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3450134316418669</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.490844739701741</v>
+        <v>2.529481436756831</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.69527224002923</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.58983977657811</v>
+        <v>-4.506073842334169</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8589799050842388</v>
+        <v>0.9171086120731231</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3066297690837157</v>
+        <v>-0.2832724961440801</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.511294378579001</v>
+        <v>2.54993107563409</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.692001268874532</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.412723446542944</v>
+        <v>-4.328957512299003</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.926555465943607</v>
+        <v>0.9846841729324916</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3066297690837157</v>
+        <v>-0.2832724961440801</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.508023407424303</v>
+        <v>2.546660104479392</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.692684660636445</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.38302132256665</v>
+        <v>-4.29925538832271</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9391197072960376</v>
+        <v>0.9972484142849221</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3110998942990291</v>
+        <v>-0.2877426213593934</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.506024724057028</v>
+        <v>2.544661421112117</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.686471635942859</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.203645901327882</v>
+        <v>-4.119879967083942</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.004656851097959</v>
+        <v>1.062785558086843</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1543231361283104</v>
+        <v>-0.1309658631886748</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.593877754265873</v>
+        <v>2.632514451320963</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.667279091274449</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.248660114848489</v>
+        <v>-4.164894180604549</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9674586210213061</v>
+        <v>1.025587328010191</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.184672031442915</v>
+        <v>-0.1613147585032794</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.5564758724087</v>
+        <v>2.59511256946379</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.672970653613395</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.515664625120924</v>
+        <v>-4.431898690876984</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8663483792512778</v>
+        <v>0.9244770862401623</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3790350694858636</v>
+        <v>-0.3556777965462279</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.445549611921877</v>
+        <v>2.484186308976966</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.672174575509896</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.616862406558097</v>
+        <v>-4.533096472314156</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8250731885729103</v>
+        <v>0.8832018955617946</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4474438830311828</v>
+        <v>-0.4240866100915471</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.403708245691187</v>
+        <v>2.442344942746276</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.820131857670783</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.584386820387325</v>
+        <v>-4.630860019247314</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9860207052021057</v>
+        <v>0.8416964383428482</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4474438830311828</v>
+        <v>-0.4240866100915471</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551665527852073</v>
+        <v>2.439944904300593</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.816656576879028</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.565348692680027</v>
+        <v>-4.611821891540017</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9901606754932695</v>
+        <v>0.8458364086340122</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5056274943623773</v>
+        <v>-0.4822702214227417</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.513280080261602</v>
+        <v>2.401559456710121</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.994238445817708</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.596475323830646</v>
+        <v>-4.642948522690635</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.155291891971703</v>
+        <v>1.010967625112445</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5056274943623773</v>
+        <v>-0.4822702214227417</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690861949200282</v>
+        <v>2.579141325648802</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.995071774803842</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.648795704431437</v>
+        <v>-4.695268903291427</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.135197068717519</v>
+        <v>0.9908728018582622</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4706806343535052</v>
+        <v>-0.4473233614138695</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.712663394191739</v>
+        <v>2.600942770640259</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.001080305200768</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.793118610356356</v>
+        <v>-4.839591809216346</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.083476436744478</v>
+        <v>0.9391521698852205</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4706806343535052</v>
+        <v>-0.4473233614138695</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.718671924588665</v>
+        <v>2.606951301037185</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.08023295299279</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.645375640121354</v>
+        <v>-4.691848838981343</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.221726272630501</v>
+        <v>1.077402005771243</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.302873277118622</v>
+        <v>-0.2795160041789864</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.898508986721617</v>
+        <v>2.786788363170137</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.083026574524271</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.747390322652575</v>
+        <v>-4.793863521512565</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.183714021149493</v>
+        <v>1.039389754290236</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.302873277118622</v>
+        <v>-0.2795160041789864</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.901302608253098</v>
+        <v>2.789581984701618</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.083688922915929</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.610780978558482</v>
+        <v>-4.657254177418472</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239020107178789</v>
+        <v>1.094695840319531</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1662639330245295</v>
+        <v>-0.1429066600848939</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.983930563101211</v>
+        <v>2.872209939549732</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489062</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.082769399656039</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.753546311381132</v>
+        <v>-4.800019510241122</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.180994450789839</v>
+        <v>1.036670183930582</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3090292658471799</v>
+        <v>-0.2856719929075443</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.897351840147731</v>
+        <v>2.785631216596252</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.14910495345286</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.69124831260501</v>
+        <v>-4.737721511465</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.272249204097109</v>
+        <v>1.127924937237851</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3090292658471799</v>
+        <v>-0.2856719929075443</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.963687393944552</v>
+        <v>2.851966770393072</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.857685825842258</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.489458114939852</v>
+        <v>-4.535931313799842</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.06154615555257</v>
+        <v>0.9172218886933126</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1110110736780255</v>
+        <v>-0.08765380073838991</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.791079181635443</v>
+        <v>2.679358558083963</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.927976058164433</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.429567433297259</v>
+        <v>-4.476040632157249</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.155792660531783</v>
+        <v>1.011468393672525</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.05112039203543206</v>
+        <v>-0.02776311909579643</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.897303822943174</v>
+        <v>2.785583199391694</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.942603794280477</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.527307977922233</v>
+        <v>-4.573781176782223</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.131324178797836</v>
+        <v>0.9869999119385791</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.06700967016841225</v>
+        <v>-0.04365239722877662</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.90239799217943</v>
+        <v>2.79067736862795</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.941139775105149</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.703645738045163</v>
+        <v>-4.750118936905152</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.059325055573336</v>
+        <v>0.915000788714079</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2433474302913416</v>
+        <v>-0.219990157351706</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.795131316930344</v>
+        <v>2.683410693378864</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.939631393145077</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.70295636588394</v>
+        <v>-4.749429564743929</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.058092422477754</v>
+        <v>0.9137681556184969</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2433474302913416</v>
+        <v>-0.219990157351706</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.793622934970272</v>
+        <v>2.681902311418793</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.939494260580513</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.709527330938532</v>
+        <v>-4.756000529798522</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.055326903891353</v>
+        <v>0.9110026370320958</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2499183953459346</v>
+        <v>-0.2265611224062989</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.789543223372953</v>
+        <v>2.677822599821473</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863228</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.939494260580513</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.784479659420873</v>
+        <v>-4.74804655950375</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.025345972498417</v>
+        <v>0.9141842251500047</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2499183953459346</v>
+        <v>-0.2265611224062989</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.789543223372953</v>
+        <v>2.677822599821473</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.719349573676941</v>
+        <v>3.580480384268512</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.813788084730972</v>
+        <v>2.656566001205793</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.784479659420873</v>
+        <v>-4.74804655950375</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.025345972498417</v>
+        <v>0.9141842251500047</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2499183953459346</v>
+        <v>-0.2265611224062989</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.80685188171734</v>
+        <v>2.649629798192161</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-29.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.5%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.4%</t>
+          <t>-625.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.8%</t>
+          <t>-280.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.0%</t>
+          <t>-141.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.6%</t>
+          <t>-258.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.1%</t>
+          <t>-184.8%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.3014133930858</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.95607874447736</v>
+        <v>-9.899216475500637</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8424678298494443</v>
+        <v>-0.8197229222587552</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.162683260615109</v>
+        <v>-2.200478932070896</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.842710135886182</v>
+        <v>1.82003273301271</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09788851868415</v>
+        <v>-10.04102624970742</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8947091850477231</v>
+        <v>-0.871964277457034</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.333962058260685</v>
+        <v>-2.371757729716472</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.744425411783272</v>
+        <v>1.7217480089098</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0244186870167</v>
+        <v>-9.967556418039976</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8499495508873229</v>
+        <v>-0.8272046432966338</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.260492226593236</v>
+        <v>-2.298287898049023</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.803879012277163</v>
+        <v>1.78120160940369</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608603</v>
+        <v>3.490059241608604</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19954310440324</v>
+        <v>-10.14268083542652</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9054440970944233</v>
+        <v>-0.8826991895037342</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.473412315435567</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.713359582592753</v>
+        <v>1.690682179719281</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410276</v>
+        <v>3.485878594410277</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43399519841773</v>
+        <v>-10.37713292944101</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.006444099601815</v>
+        <v>-0.9836991920111262</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.473412315435567</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.706140417691157</v>
+        <v>1.683463014817685</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764401</v>
+        <v>3.480692492764402</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.66493677397825</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.105492920599997</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.723420488517018</v>
+        <v>-2.761216159972805</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526785920194838</v>
+        <v>1.504108517321366</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371601439059</v>
+        <v>3.493716014390592</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.71772292957857</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.125491593001572</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.819095975099415</v>
+        <v>-2.856891646555202</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.470496418083956</v>
+        <v>1.447819015210484</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297404</v>
+        <v>3.492101641297406</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-10.94975184931484</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.215609432266962</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.918904343743626</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.435982528400017</v>
+        <v>1.413305125526545</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322548</v>
+        <v>3.57367402532255</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-10.89773633534602</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.190812890993036</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.918904343743626</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.439972864086418</v>
+        <v>1.417295461212946</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158926</v>
+        <v>3.600038265158927</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-11.03940817707014</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.248956854581426</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.918904343743626</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.438497637187676</v>
+        <v>1.415820234314204</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-10.98981733264531</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.21406710664662</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.831517827863005</v>
+        <v>-2.869313499318792</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.483305554007449</v>
+        <v>1.460628151133976</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.79066522540821</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.147457397398463</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.666195301913191</v>
+        <v>-2.703990973368978</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.569447935930654</v>
+        <v>1.546770533057181</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.5648200726888</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.04754026327449</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.662064297781815</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.60418301431916</v>
+        <v>1.581505611445688</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.44024141635121</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-0.9965696561833952</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.662064297781815</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.605322158875219</v>
+        <v>1.582644756001747</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.49313670439549</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-1.015093997239002</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.657108951693369</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.610929140690395</v>
+        <v>1.588251737816923</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.20922797346675</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.8957968006288661</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.657108951693369</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.616662844929031</v>
+        <v>1.593985442055559</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.1378615808571</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.8769875059788719</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.585742559083721</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.649745418100955</v>
+        <v>1.627068015227483</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-9.874024713653029</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.7813362404101518</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.585742559083721</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.639861936788047</v>
+        <v>1.617184533914575</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.606782912784631</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.6762740805621665</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.585742559083721</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.638027376288673</v>
+        <v>1.615349973415201</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.50887587410814</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.6374115800650308</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.479961137767377</v>
+        <v>-2.517756809223164</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.678518511231546</v>
+        <v>1.655841108358074</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.484922333132182</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.6271616575291543</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.45600759679142</v>
+        <v>-2.493803268247207</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.693559141962615</v>
+        <v>1.670881739089142</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.220862394809386</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.5347979983617877</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.229743329924411</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.83873478879454</v>
+        <v>1.816057385921068</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.513782771304548</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.2547531826201537</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.229743329924411</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.835947755134239</v>
+        <v>1.813270352260767</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.473598472938358</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.2383358393858361</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.151763360102433</v>
+        <v>-2.18955903155822</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.860401958041795</v>
+        <v>1.837724555168323</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.393528677400553</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.2069410999499572</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.071693564564629</v>
+        <v>-2.109489236020416</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.907810656585234</v>
+        <v>1.885133253711762</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.160047455170954</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.1056241822202653</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.838212342335031</v>
+        <v>-1.876008013790817</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.055823818760846</v>
+        <v>2.033146415887374</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-8.01038106416344</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.04864983613021856</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.745308851092495</v>
+        <v>-1.783104522548282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.108673703193408</v>
+        <v>2.085996300319936</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-7.878105590532553</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>-0.0003721599308370571</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.613033377461608</v>
+        <v>-1.650829048917395</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.183406474118967</v>
+        <v>2.160729071245495</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105958</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.687505915859401</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>0.07868277062606088</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.460229374244242</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.277903936737023</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960993</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.43850611717582</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.1911890313231521</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.460229374244242</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.290810277960682</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.544096106948924</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>0.02097710581469148</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.565819364017346</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.099480354497601</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.562831009067521</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>0.06202748684433912</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.565819364017346</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.148024696374687</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.414890967659922</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>0.001324580719211266</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.545498448108789</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>2.040338323231654</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.397732817528627</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>-0.0005261454817491185</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.528340297977494</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>2.041919227056953</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.354184410757937</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>0.009932605131433903</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.528340297977494</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>2.03495861496186</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.112036017304079</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.1212543168941203</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.528340297977494</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>2.049420969343003</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722823</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.105668914512453</v>
+        <v>-7.048806645535731</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1183332784699656</v>
+        <v>0.1410781860606543</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.528340297977494</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>2.043953089802198</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792053</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.982377779695322</v>
+        <v>-6.9255155107186</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1651478264073947</v>
+        <v>0.1878927339980838</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.405049163160364</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.115425864703053</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919915</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.961228580791879</v>
+        <v>-6.904366311815156</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.181308484206097</v>
+        <v>0.2040533917967862</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.383899964256921</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.135816362282444</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.7483284083181</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717463138808434</v>
+        <v>-6.660600869831712</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2745953693465255</v>
+        <v>0.2973402769372147</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.383899964256921</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.131597070629495</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.570566111090564</v>
+        <v>-6.513703842113841</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3354784943536897</v>
+        <v>0.3582234019443788</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.336241722278332</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.162316329736663</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.320715717141489</v>
+        <v>-6.263853448164767</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4281607269170218</v>
+        <v>0.4509056345077109</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.336241722278332</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.155058404720366</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.144823624674057</v>
+        <v>-6.087961355697335</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5021166874246434</v>
+        <v>0.5248615950153326</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.336241722278332</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.158657528241014</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.973377161651594</v>
+        <v>-5.916514892674871</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5840227786881824</v>
+        <v>0.6067676862788716</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.164795259255869</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.274852912109046</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.748344161982771</v>
+        <v>-5.691481893006048</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6730564561720089</v>
+        <v>0.6958013637626976</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-0.9397622595870466</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.408893189526637</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.684708419748836</v>
+        <v>-5.627846150772114</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7032055541198998</v>
+        <v>0.725950461710589</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8761265173531121</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.451769435921315</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.591708378542938</v>
+        <v>-5.534846109566216</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7215998293860548</v>
+        <v>0.7443447369767435</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8761265173531121</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.43296369470511</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.351277881738078</v>
+        <v>-5.294415612761355</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8195151047328761</v>
+        <v>0.8422600123235653</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6356960205482518</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.578965069412904</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.279035313566883</v>
+        <v>-5.222173044590161</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8523414458361742</v>
+        <v>0.8750863534268634</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.6356960205482518</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.582894383247724</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.226036991285495</v>
+        <v>-5.169174722308773</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8742193586660694</v>
+        <v>0.8969642662567585</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.580359761546313</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.616774722566227</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.117232105805768</v>
+        <v>-5.060369836829046</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9147393840779539</v>
+        <v>0.9374842916686426</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.580359761546313</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.613772793786221</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897211307768758</v>
+        <v>-4.840349038792035</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004326740303372</v>
+        <v>1.027071647894061</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.4391399164783327</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.700083737837623</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.76434361870548</v>
+        <v>-4.707481349728758</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073367998730506</v>
+        <v>1.096112906321195</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.4391399164783327</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.715977920639447</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.60482851518611</v>
+        <v>-4.547966246209388</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138319884578556</v>
+        <v>1.161064792169245</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.2796248129589628</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.81283282719137</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460156370086373</v>
+        <v>-4.40329410110965</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206276845179891</v>
+        <v>1.22902175277058</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.1349526678592254</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.909724216812652</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.520031197444065</v>
+        <v>-4.463168928467343</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16836440563824</v>
+        <v>1.191109313228929</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1948274952169175</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.859836811799463</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433231699665056</v>
+        <v>-4.376369430688333</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.22548469807241</v>
+        <v>1.248229605663099</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1948274952169175</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.882237305122029</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435701406126862</v>
+        <v>-4.378839137150139</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.2245692168611</v>
+        <v>1.247314124451788</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.1972972016787237</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.880827882618358</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504071592450872</v>
+        <v>-4.44720932347415</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208228064806197</v>
+        <v>1.230972972396887</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1880215026425087</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.897400224514789</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612609773367006</v>
+        <v>-4.555747504390284</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155249501071635</v>
+        <v>1.177994408662324</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1880215026425087</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.88783693314668</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643602932695711</v>
+        <v>-4.586740663718989</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9675618023805399</v>
+        <v>0.9903067099712288</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1880215026425087</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.712546498187067</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468128672903243</v>
+        <v>-4.41126640392652</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042318738289315</v>
+        <v>1.065063645880004</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1880215026425087</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.717113730178855</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579064925544492</v>
+        <v>-4.522202656567769</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9736862659940226</v>
+        <v>0.9964311735847116</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1880215026425087</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.692855758940062</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782091503087725</v>
+        <v>-4.725229234111002</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8956070201966349</v>
+        <v>0.9183519277873238</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3910480801857421</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.574171197634027</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624165904152432</v>
+        <v>-4.567303635175709</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689496462028844</v>
+        <v>0.9916945537935735</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3910480801857421</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.584343584066159</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.481060172149331</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983933019872959</v>
+        <v>1.021138209577985</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3910480801857421</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.57928985464002</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.539105525777115</v>
+        <v>-4.482243256800393</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9896958435713969</v>
+        <v>1.012440751162086</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3588954571964666</v>
+        <v>-0.3966911286522536</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.59035720387811</v>
+        <v>2.567679801004638</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.415977818783032</v>
+        <v>-4.35911554980631</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.039498799402132</v>
+        <v>1.062243706992821</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3588954571964666</v>
+        <v>-0.3966911286522536</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.590909076911212</v>
+        <v>2.56823167403774</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809504</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.323167337332173</v>
+        <v>-4.26630506835545</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.005895683873841</v>
+        <v>1.02864059146453</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2660849757456073</v>
+        <v>-0.3038806472013943</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.575868057673093</v>
+        <v>2.553190654799621</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.274604285111143</v>
+        <v>-4.21774201613442</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.027194380686854</v>
+        <v>1.049939288277543</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2175219235245771</v>
+        <v>-0.2553175949803641</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.606879364930312</v>
+        <v>2.58420196205684</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.161933066874893</v>
+        <v>-4.10507079789817</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.067338576493077</v>
+        <v>1.090083484083766</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1048507052883269</v>
+        <v>-0.1426463767441139</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.669557804383786</v>
+        <v>2.646880401510313</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.04955606569222</v>
+        <v>-3.992693796715498</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117780672796813</v>
+        <v>1.140525580387502</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1048507052883269</v>
+        <v>-0.1426463767441139</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.675049100214453</v>
+        <v>2.652371697340981</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.24779063457895</v>
+        <v>-4.190928365602228</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.04998404701066</v>
+        <v>1.072728954601349</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3030852741750575</v>
+        <v>-0.3408809456308445</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.567605560650954</v>
+        <v>2.544928157777481</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.330791915604229</v>
+        <v>-4.273929646627507</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8551392546012018</v>
+        <v>0.8778841621918909</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3594518301580182</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.394818749935302</v>
+        <v>2.37214134706183</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.457858921911217</v>
+        <v>-4.400996652934495</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9244621127976123</v>
+        <v>0.9472070203883012</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3594518301580182</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.514968410654508</v>
+        <v>2.492291007781036</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.54445750489232</v>
+        <v>-4.487595235915598</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9043357057074941</v>
+        <v>0.927080613298183</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3216561587022312</v>
+        <v>-0.3594518301580182</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.529481436756831</v>
+        <v>2.506804033883359</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.506073842334169</v>
+        <v>-4.449211573357447</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9171086120731231</v>
+        <v>0.9398535196638123</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2832724961440801</v>
+        <v>-0.3210681675998671</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.54993107563409</v>
+        <v>2.527253672760618</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.328957512299003</v>
+        <v>-4.272095243322281</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9846841729324916</v>
+        <v>1.00742908052318</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2832724961440801</v>
+        <v>-0.3210681675998671</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.546660104479392</v>
+        <v>2.52398270160592</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.29925538832271</v>
+        <v>-4.242393119345987</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9972484142849221</v>
+        <v>1.019993321875611</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2877426213593934</v>
+        <v>-0.3255382928151804</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.544661421112117</v>
+        <v>2.521984018238645</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.119879967083942</v>
+        <v>-4.063017698107219</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.062785558086843</v>
+        <v>1.085530465677532</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1309658631886748</v>
+        <v>-0.1687615346444618</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.632514451320963</v>
+        <v>2.609837048447491</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.164894180604549</v>
+        <v>-4.108031911627826</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.025587328010191</v>
+        <v>1.04833223560088</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1613147585032794</v>
+        <v>-0.1991104299590664</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.59511256946379</v>
+        <v>2.572435166590318</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.431898690876984</v>
+        <v>-4.375036421900261</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9244770862401623</v>
+        <v>0.9472219938308513</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3556777965462279</v>
+        <v>-0.3934734680020149</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.484186308976966</v>
+        <v>2.461508906103494</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.533096472314156</v>
+        <v>-4.476234203337434</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8832018955617946</v>
+        <v>0.9059468031524838</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4240866100915471</v>
+        <v>-0.4618822815473341</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.442344942746276</v>
+        <v>2.419667539872804</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.630860019247314</v>
+        <v>-4.443758617166662</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8416964383428482</v>
+        <v>0.9165369991751093</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4240866100915471</v>
+        <v>-0.4618822815473341</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.439944904300593</v>
+        <v>2.417267501427121</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.611821891540017</v>
+        <v>-4.424720489459364</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8458364086340122</v>
+        <v>0.9206769694662731</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4822702214227417</v>
+        <v>-0.5200658928785287</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.401559456710121</v>
+        <v>2.378882053836649</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.642948522690635</v>
+        <v>-4.455847120609983</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.010967625112445</v>
+        <v>1.085808185944706</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4822702214227417</v>
+        <v>-0.5200658928785287</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.579141325648802</v>
+        <v>2.55646392277533</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.695268903291427</v>
+        <v>-4.508167501210774</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9908728018582622</v>
+        <v>1.065713362690523</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4473233614138695</v>
+        <v>-0.4851190328696565</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.600942770640259</v>
+        <v>2.578265367766787</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.839591809216346</v>
+        <v>-4.652490407135693</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9391521698852205</v>
+        <v>1.013992730717482</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4473233614138695</v>
+        <v>-0.4851190328696565</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.606951301037185</v>
+        <v>2.584273898163713</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.691848838981343</v>
+        <v>-4.504747436900691</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.077402005771243</v>
+        <v>1.152242566603505</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2795160041789864</v>
+        <v>-0.3173116756347734</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.786788363170137</v>
+        <v>2.764110960296664</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.793863521512565</v>
+        <v>-4.606762119431912</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.039389754290236</v>
+        <v>1.114230315122497</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2795160041789864</v>
+        <v>-0.3173116756347734</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.789581984701618</v>
+        <v>2.766904581828145</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.657254177418472</v>
+        <v>-4.470152775337819</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.094695840319531</v>
+        <v>1.169536401151792</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1429066600848939</v>
+        <v>-0.1807023315406809</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.872209939549732</v>
+        <v>2.849532536676259</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489062</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.800019510241122</v>
+        <v>-4.61291810816047</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.036670183930582</v>
+        <v>1.111510744762843</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2856719929075443</v>
+        <v>-0.3234676643633313</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.785631216596252</v>
+        <v>2.762953813722779</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.737721511465</v>
+        <v>-4.550620109384347</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.127924937237851</v>
+        <v>1.202765498070112</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2856719929075443</v>
+        <v>-0.3234676643633313</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.851966770393072</v>
+        <v>2.8292893675196</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.535931313799842</v>
+        <v>-4.348829911719189</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9172218886933126</v>
+        <v>0.9920624495255737</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.08765380073838991</v>
+        <v>-0.1254494721941769</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.679358558083963</v>
+        <v>2.656681155210491</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.476040632157249</v>
+        <v>-4.288939230076596</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011468393672525</v>
+        <v>1.086308954504786</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.02776311909579643</v>
+        <v>-0.06555879055158342</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.785583199391694</v>
+        <v>2.762905796518222</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.573781176782223</v>
+        <v>-4.38667977470157</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9869999119385791</v>
+        <v>1.06184047277084</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.04365239722877662</v>
+        <v>-0.08144806868456361</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.79067736862795</v>
+        <v>2.767999965754477</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.750118936905152</v>
+        <v>-4.5630175348245</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.915000788714079</v>
+        <v>0.9898413495463401</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.219990157351706</v>
+        <v>-0.257785828807493</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.683410693378864</v>
+        <v>2.660733290505392</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.749429564743929</v>
+        <v>-4.562328162663277</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9137681556184969</v>
+        <v>0.9886087164507578</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.219990157351706</v>
+        <v>-0.257785828807493</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.681902311418793</v>
+        <v>2.65922490854532</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.756000529798522</v>
+        <v>-4.568899127717869</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9110026370320958</v>
+        <v>0.9858431978643569</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.2643567938620859</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.677822599821473</v>
+        <v>2.655145196948001</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.74804655950375</v>
+        <v>-4.560945157423097</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9141842251500047</v>
+        <v>0.9890247859822658</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.2643567938620859</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.677822599821473</v>
+        <v>2.655145196948001</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.580480384268512</v>
+        <v>3.784133270442421</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.656566001205793</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.74804655950375</v>
+        <v>-4.643480359453062</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9141842251500047</v>
+        <v>0.9623924621980844</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2265611224062989</v>
+        <v>-0.3468919958920515</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.649629798192161</v>
+        <v>2.612005832757826</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240528.xlsx
+++ b/tame_output/ON/bt/strategyON_20240528.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.2%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.9%</t>
+          <t>-617.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.0%</t>
+          <t>-274.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-141.6%</t>
+          <t>-141.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-258.7%</t>
+          <t>-250.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.8%</t>
+          <t>-177.5%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612276</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.3014133930858</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355691</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608604</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410277</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764402</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390592</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297406</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532255</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158927</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105958</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960993</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.397732817528627</v>
+        <v>-7.395183080444112</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0005261454817491185</v>
+        <v>0.0004937493520569269</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.528340297977494</v>
+        <v>-1.525790560892979</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.041919227056953</v>
+        <v>2.043449069307662</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.354184410757937</v>
+        <v>-7.351634673673422</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.009932605131433903</v>
+        <v>0.01095249996523995</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.528340297977494</v>
+        <v>-1.525790560892979</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.03495861496186</v>
+        <v>2.036488457212569</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.112036017304079</v>
+        <v>-7.109486280219564</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1212543168941203</v>
+        <v>0.1222742117279263</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.528340297977494</v>
+        <v>-1.525790560892979</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.049420969343003</v>
+        <v>2.050950811593712</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722823</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.048806645535731</v>
+        <v>-7.046256908451215</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1410781860606543</v>
+        <v>0.1420980808944607</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.528340297977494</v>
+        <v>-1.525790560892979</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.043953089802198</v>
+        <v>2.045482932052907</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792053</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.9255155107186</v>
+        <v>-6.922965773634084</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1878927339980838</v>
+        <v>0.1889126288318899</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.405049163160364</v>
+        <v>-1.402499426075849</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.115425864703053</v>
+        <v>2.116955706953762</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919915</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.904366311815156</v>
+        <v>-6.901816574730641</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2040533917967862</v>
+        <v>0.2050732866305922</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.383899964256921</v>
+        <v>-1.381350227172405</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.135816362282444</v>
+        <v>2.137346204533153</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.7483284083181</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.660600869831712</v>
+        <v>-6.658051132747197</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2973402769372147</v>
+        <v>0.2983601717710207</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.383899964256921</v>
+        <v>-1.381350227172405</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.131597070629495</v>
+        <v>2.133126912880204</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.513703842113841</v>
+        <v>-6.511154105029327</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3582234019443788</v>
+        <v>0.3592432967781845</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.336241722278332</v>
+        <v>-1.333691985193817</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.162316329736663</v>
+        <v>2.163846171987373</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.263853448164767</v>
+        <v>-6.261303711080252</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4509056345077109</v>
+        <v>0.4519255293415165</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.336241722278332</v>
+        <v>-1.333691985193817</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.155058404720366</v>
+        <v>2.156588246971075</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.087961355697335</v>
+        <v>-6.08541161861282</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5248615950153326</v>
+        <v>0.5258814898491382</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.336241722278332</v>
+        <v>-1.333691985193817</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.158657528241014</v>
+        <v>2.160187370491724</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.916514892674871</v>
+        <v>-5.913965155590357</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6067676862788716</v>
+        <v>0.6077875811126772</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.164795259255869</v>
+        <v>-1.162245522171354</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.274852912109046</v>
+        <v>2.276382754359755</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.691481893006048</v>
+        <v>-5.688932155921534</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6958013637626976</v>
+        <v>0.6968212585965037</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9397622595870466</v>
+        <v>-0.9372125225025313</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.408893189526637</v>
+        <v>2.410423031777346</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.627846150772114</v>
+        <v>-5.625296413687599</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.725950461710589</v>
+        <v>0.7269703565443946</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8761265173531121</v>
+        <v>-0.8735767802685968</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.451769435921315</v>
+        <v>2.453299278172024</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.534846109566216</v>
+        <v>-5.532296372481701</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7443447369767435</v>
+        <v>0.7453646318105496</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8761265173531121</v>
+        <v>-0.8735767802685968</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.43296369470511</v>
+        <v>2.43449353695582</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.294415612761355</v>
+        <v>-5.291865875676841</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8422600123235653</v>
+        <v>0.8432799071573709</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6356960205482518</v>
+        <v>-0.6331462834637365</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.578965069412904</v>
+        <v>2.580494911663613</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.222173044590161</v>
+        <v>-5.219623307505646</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8750863534268634</v>
+        <v>0.876106248260669</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6356960205482518</v>
+        <v>-0.6331462834637365</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.582894383247724</v>
+        <v>2.584424225498433</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169174722308773</v>
+        <v>-5.166624985224258</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8969642662567585</v>
+        <v>0.8979841610905641</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.580359761546313</v>
+        <v>-0.5778100244617976</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.616774722566227</v>
+        <v>2.618304564816937</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.060369836829046</v>
+        <v>-5.057820099744531</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9374842916686426</v>
+        <v>0.9385041865024486</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.580359761546313</v>
+        <v>-0.5778100244617976</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.613772793786221</v>
+        <v>2.61530263603693</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.840349038792035</v>
+        <v>-4.837799301707521</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.027071647894061</v>
+        <v>1.028091542727867</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4391399164783327</v>
+        <v>-0.4365901793938174</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.700083737837623</v>
+        <v>2.701613580088332</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.707481349728758</v>
+        <v>-4.704931612644243</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.096112906321195</v>
+        <v>1.097132801155001</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4391399164783327</v>
+        <v>-0.4365901793938174</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.715977920639447</v>
+        <v>2.717507762890155</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.547966246209388</v>
+        <v>-4.545416509124873</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.161064792169245</v>
+        <v>1.162084687003051</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2796248129589628</v>
+        <v>-0.2770750758744475</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.81283282719137</v>
+        <v>2.81436266944208</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.40329410110965</v>
+        <v>-4.400744364025136</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22902175277058</v>
+        <v>1.230041647604386</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1349526678592254</v>
+        <v>-0.13240293077471</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.909724216812652</v>
+        <v>2.911254059063362</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.463168928467343</v>
+        <v>-4.460619191382828</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.191109313228929</v>
+        <v>1.192129208062735</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1948274952169175</v>
+        <v>-0.1922777581324022</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.859836811799463</v>
+        <v>2.861366654050172</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.376369430688333</v>
+        <v>-4.373819693603819</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.248229605663099</v>
+        <v>1.249249500496905</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1948274952169175</v>
+        <v>-0.1922777581324022</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.882237305122029</v>
+        <v>2.883767147372738</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.378839137150139</v>
+        <v>-4.376289400065625</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.247314124451788</v>
+        <v>1.248334019285594</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1972972016787237</v>
+        <v>-0.1947474645942083</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.880827882618358</v>
+        <v>2.882357724869067</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.44720932347415</v>
+        <v>-4.444659586389635</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.230972972396887</v>
+        <v>1.231992867230692</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1880215026425087</v>
+        <v>-0.1854717655579934</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.897400224514789</v>
+        <v>2.898930066765498</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.555747504390284</v>
+        <v>-4.553197767305769</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177994408662324</v>
+        <v>1.17901430349613</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1880215026425087</v>
+        <v>-0.1854717655579934</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88783693314668</v>
+        <v>2.889366775397389</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.586740663718989</v>
+        <v>-4.584190926634474</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9903067099712288</v>
+        <v>0.9913266048050347</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1880215026425087</v>
+        <v>-0.1854717655579934</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.712546498187067</v>
+        <v>2.714076340437776</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.41126640392652</v>
+        <v>-4.408716666842006</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.065063645880004</v>
+        <v>1.06608354071381</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1880215026425087</v>
+        <v>-0.1854717655579934</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717113730178855</v>
+        <v>2.718643572429563</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.522202656567769</v>
+        <v>-4.519652919483255</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9964311735847116</v>
+        <v>0.9974510684185174</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1880215026425087</v>
+        <v>-0.1854717655579934</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.692855758940062</v>
+        <v>2.694385601190771</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.725229234111002</v>
+        <v>-4.722679497026488</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9183519277873238</v>
+        <v>0.9193718226211296</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3910480801857421</v>
+        <v>-0.3884983431012268</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.574171197634027</v>
+        <v>2.575701039884736</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.567303635175709</v>
+        <v>-4.564753898091195</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9916945537935735</v>
+        <v>0.9927144486273791</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3910480801857421</v>
+        <v>-0.3884983431012268</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.584343584066159</v>
+        <v>2.585873426316869</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.481060172149331</v>
+        <v>-4.478510435064817</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.021138209577985</v>
+        <v>1.022158104411791</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3910480801857421</v>
+        <v>-0.3884983431012268</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.57928985464002</v>
+        <v>2.580819696890729</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.482243256800393</v>
+        <v>-4.479693519715878</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.012440751162086</v>
+        <v>1.013460645995892</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3966911286522536</v>
+        <v>-0.3941413915677383</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.567679801004638</v>
+        <v>2.569209643255348</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.35911554980631</v>
+        <v>-4.356565812721795</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.062243706992821</v>
+        <v>1.063263601826626</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3966911286522536</v>
+        <v>-0.3941413915677383</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.56823167403774</v>
+        <v>2.569761516288449</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.26630506835545</v>
+        <v>-4.263755331270936</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.02864059146453</v>
+        <v>1.029660486298336</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3038806472013943</v>
+        <v>-0.301330910116879</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.553190654799621</v>
+        <v>2.55472049705033</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.21774201613442</v>
+        <v>-4.215192279049906</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.049939288277543</v>
+        <v>1.050959183111349</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2553175949803641</v>
+        <v>-0.2527678578958488</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.58420196205684</v>
+        <v>2.585731804307549</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.10507079789817</v>
+        <v>-4.102521060813656</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.090083484083766</v>
+        <v>1.091103378917572</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1426463767441139</v>
+        <v>-0.1400966396595986</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.646880401510313</v>
+        <v>2.648410243761023</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.992693796715498</v>
+        <v>-3.990144059630983</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.140525580387502</v>
+        <v>1.141545475221308</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1426463767441139</v>
+        <v>-0.1400966396595986</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.652371697340981</v>
+        <v>2.65390153959169</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.190928365602228</v>
+        <v>-4.188378628517714</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.072728954601349</v>
+        <v>1.073748849435155</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3408809456308445</v>
+        <v>-0.3383312085463291</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.544928157777481</v>
+        <v>2.54645800002819</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.273929646627507</v>
+        <v>-4.271379909542993</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8778841621918909</v>
+        <v>0.8789040570256965</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3594518301580182</v>
+        <v>-0.3569020930735029</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.37214134706183</v>
+        <v>2.373671189312539</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.400996652934495</v>
+        <v>-4.398446915849981</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9472070203883012</v>
+        <v>0.948226915222107</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3594518301580182</v>
+        <v>-0.3569020930735029</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.492291007781036</v>
+        <v>2.493820850031745</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.487595235915598</v>
+        <v>-4.485045498831083</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.927080613298183</v>
+        <v>0.9281005081319889</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3594518301580182</v>
+        <v>-0.3569020930735029</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.506804033883359</v>
+        <v>2.508333876134068</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.449211573357447</v>
+        <v>-4.446661836272932</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9398535196638123</v>
+        <v>0.9408734144976179</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3210681675998671</v>
+        <v>-0.3185184305153517</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.527253672760618</v>
+        <v>2.528783515011328</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.272095243322281</v>
+        <v>-4.269545506237766</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.00742908052318</v>
+        <v>1.008448975356986</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3210681675998671</v>
+        <v>-0.3185184305153517</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.52398270160592</v>
+        <v>2.525512543856629</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.242393119345987</v>
+        <v>-4.239843382261473</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.019993321875611</v>
+        <v>1.021013216709417</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3255382928151804</v>
+        <v>-0.3229885557306651</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.521984018238645</v>
+        <v>2.523513860489354</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.063017698107219</v>
+        <v>-4.060467961022705</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.085530465677532</v>
+        <v>1.086550360511338</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1687615346444618</v>
+        <v>-0.1662117975599464</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.609837048447491</v>
+        <v>2.6113668906982</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.108031911627826</v>
+        <v>-4.105482174543312</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04833223560088</v>
+        <v>1.049352130434685</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1991104299590664</v>
+        <v>-0.196560692874551</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.572435166590318</v>
+        <v>2.573965008841027</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.375036421900261</v>
+        <v>-4.372486684815747</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9472219938308513</v>
+        <v>0.9482418886646571</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3934734680020149</v>
+        <v>-0.3909237309174996</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.461508906103494</v>
+        <v>2.463038748354204</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.476234203337434</v>
+        <v>-4.473684466252919</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9059468031524838</v>
+        <v>0.9069666979862894</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4618822815473341</v>
+        <v>-0.4593325444628188</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.419667539872804</v>
+        <v>2.421197382123514</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.443758617166662</v>
+        <v>-4.441208880082147</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9165369991751093</v>
+        <v>0.9175568940089152</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4618822815473341</v>
+        <v>-0.4593325444628188</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.417267501427121</v>
+        <v>2.41879734367783</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.424720489459364</v>
+        <v>-4.42217075237485</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9206769694662731</v>
+        <v>0.9216968643000789</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5200658928785287</v>
+        <v>-0.5175161557940133</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.378882053836649</v>
+        <v>2.380411896087359</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.455847120609983</v>
+        <v>-4.453297383525468</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.085808185944706</v>
+        <v>1.086828080778512</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5200658928785287</v>
+        <v>-0.5175161557940133</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55646392277533</v>
+        <v>2.557993765026039</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.508167501210774</v>
+        <v>-4.50561776412626</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.065713362690523</v>
+        <v>1.066733257524329</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4851190328696565</v>
+        <v>-0.4825692957851412</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.578265367766787</v>
+        <v>2.579795210017496</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.652490407135693</v>
+        <v>-4.649940670051179</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.013992730717482</v>
+        <v>1.015012625551287</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4851190328696565</v>
+        <v>-0.4825692957851412</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.584273898163713</v>
+        <v>2.585803740414422</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.504747436900691</v>
+        <v>-4.502197699816176</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.152242566603505</v>
+        <v>1.15326246143731</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3173116756347734</v>
+        <v>-0.314761938550258</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.764110960296664</v>
+        <v>2.765640802547374</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.606762119431912</v>
+        <v>-4.604212382347398</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.114230315122497</v>
+        <v>1.115250209956303</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3173116756347734</v>
+        <v>-0.314761938550258</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.766904581828145</v>
+        <v>2.768434424078855</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.470152775337819</v>
+        <v>-4.467603038253305</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.169536401151792</v>
+        <v>1.170556295985598</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1807023315406809</v>
+        <v>-0.1781525944561655</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.849532536676259</v>
+        <v>2.851062378926968</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489062</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.61291810816047</v>
+        <v>-4.610368371075955</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.111510744762843</v>
+        <v>1.112530639596648</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3234676643633313</v>
+        <v>-0.320917927278816</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.762953813722779</v>
+        <v>2.764483655973488</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.550620109384347</v>
+        <v>-4.548070372299833</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.202765498070112</v>
+        <v>1.203785392903918</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3234676643633313</v>
+        <v>-0.320917927278816</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.8292893675196</v>
+        <v>2.830819209770309</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.348829911719189</v>
+        <v>-4.346280174634675</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9920624495255737</v>
+        <v>0.9930823443593795</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1254494721941769</v>
+        <v>-0.1228997351096616</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.656681155210491</v>
+        <v>2.6582109974612</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.288939230076596</v>
+        <v>-4.286389492992082</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.086308954504786</v>
+        <v>1.087328849338592</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06555879055158342</v>
+        <v>-0.06300905346706809</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.762905796518222</v>
+        <v>2.764435638768931</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.38667977470157</v>
+        <v>-4.384130037617056</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.06184047277084</v>
+        <v>1.062860367604646</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.08144806868456361</v>
+        <v>-0.07889833160004828</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.767999965754477</v>
+        <v>2.769529808005187</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.5630175348245</v>
+        <v>-4.560467797739985</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9898413495463401</v>
+        <v>0.9908612443801457</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.257785828807493</v>
+        <v>-0.2552360917229777</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.660733290505392</v>
+        <v>2.662263132756101</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.562328162663277</v>
+        <v>-4.559778425578762</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9886087164507578</v>
+        <v>0.9896286112845636</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.257785828807493</v>
+        <v>-0.2552360917229777</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.65922490854532</v>
+        <v>2.660754750796029</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.568899127717869</v>
+        <v>-4.566349390633355</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9858431978643569</v>
+        <v>0.9868630926981627</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2643567938620859</v>
+        <v>-0.2618070567775706</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.655145196948001</v>
+        <v>2.65667503919871</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.560945157423097</v>
+        <v>-4.558395420338583</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9890247859822658</v>
+        <v>0.9900446808160717</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2643567938620859</v>
+        <v>-0.2618070567775706</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.655145196948001</v>
+        <v>2.65667503919871</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.784133270442421</v>
+        <v>3.837995487067473</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.843298104683162</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.643480359453062</v>
+        <v>-4.560384270128004</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9623924621980844</v>
+        <v>1.018787972318213</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3468919958920515</v>
+        <v>-0.263795906566992</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.612005832757826</v>
+        <v>2.685020560742967</v>
       </c>
     </row>
   </sheetData>
